--- a/product_order_forms/030_thoughts_on_airpods--product_order_forms.xlsx
+++ b/product_order_forms/030_thoughts_on_airpods--product_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FirstName</t>
+          <t>What is your first name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>airpods_like</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HowDoYouLikeAirpods</t>
+          <t>How do you like Airpods?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LastName</t>
+          <t>What is your last name?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WhatsYourFavoriteFeature</t>
+          <t>What is your favorite feature of Airpods?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>favorite_feature</t>
+          <t>features</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WhatsYourFavoriteFeature</t>
+          <t>Which of the following features do you like most?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>how_long</t>
+          <t>usage_duration</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HowLongYouWillUseAirpods</t>
+          <t>How long do you plan to use Airpods for?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>why_buy</t>
+          <t>purchase_reason</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WhyDoYouWantToBuyAirpods</t>
+          <t>Why do you want to buy Airpods?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
+          <t>satisfaction</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HowSatisfied</t>
+          <t>How satisfied are you with Airpods?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Do you have any comments about Airpods?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>favorite_color</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Firstname</t>
+          <t>What is your favorite Airpods color?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>design_pleasing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lastname</t>
+          <t>Do you like the design of Airpods?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>durability</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>How long do you think Airpods will last?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Do you have any other comments about Airpods?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -964,7 +964,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>features_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>features_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -998,7 +998,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>features_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>favorite_feature_choices</t>
+          <t>features_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1032,7 +1032,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,7 +1049,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
